--- a/data/trans_dic/P41D_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,63</t>
+          <t>0,0; 87,03</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,5</t>
+          <t>0,0; 78,88</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,24; 60,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,58; 43,3</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 51,42</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8,48; 64,97</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5,48; 43,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,7 +981,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1042,7 +991,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>0; 3971</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1059,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1381</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1381</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1127,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2473</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1137,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2473</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1210,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4710</t>
+          <t>0; 4504</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1121</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 817</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1282</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4154</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6044</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>831; 6065</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1190; 9230</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>4154</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>0; 5776</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>855; 6551</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1167; 9247</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P41D_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Clase-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,03</t>
+          <t>0,0; 86,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,88</t>
+          <t>0,0; 83,16</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,8</t>
+          <t>0,0; 50,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 60,15</t>
+          <t>7,84; 58,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 43,3</t>
+          <t>4,96; 42,76</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2073</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 2735</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3971</t>
+          <t>0; 4071</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>771</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2033</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 3558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2193</t>
+          <t>0; 2168</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4504</t>
+          <t>0; 4763</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4106</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6044</t>
+          <t>0; 6024</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>831; 6065</t>
+          <t>811; 6073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1190; 9230</t>
+          <t>1103; 9511</t>
         </is>
       </c>
     </row>
